--- a/diseases/d031/2015-2019.xlsx
+++ b/diseases/d031/2015-2019.xlsx
@@ -1288,9 +1288,6 @@
       <c r="O5" t="n">
         <v>594</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>1.165073417326954</v>
       </c>
@@ -1959,9 +1956,6 @@
       <c r="O9" t="n">
         <v>473</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.9277436471307229</v>
       </c>
@@ -2630,9 +2624,6 @@
       <c r="O13" t="n">
         <v>585</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>1.147420789791697</v>
       </c>
@@ -3301,9 +3292,6 @@
       <c r="O17" t="n">
         <v>646</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>1.26706637641955</v>
       </c>
@@ -3972,9 +3960,6 @@
       <c r="O21" t="n">
         <v>662</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>1.298448825371117</v>
       </c>
@@ -4643,9 +4628,6 @@
       <c r="O25" t="n">
         <v>575</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>1.127806759196967</v>
       </c>
@@ -5314,9 +5296,6 @@
       <c r="O29" t="n">
         <v>530</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>1.039543621520683</v>
       </c>
@@ -5985,9 +5964,6 @@
       <c r="O33" t="n">
         <v>298</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.5844981117229501</v>
       </c>
@@ -6656,9 +6632,6 @@
       <c r="O37" t="n">
         <v>351</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.6884524738750184</v>
       </c>
@@ -7327,9 +7300,6 @@
       <c r="O41" t="n">
         <v>440</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.8630173461681142</v>
       </c>
@@ -7998,9 +7968,6 @@
       <c r="O45" t="n">
         <v>771</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>1.512241758853673</v>
       </c>
@@ -8669,9 +8636,6 @@
       <c r="O49" t="n">
         <v>1077</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>2.112431095052407</v>
       </c>
@@ -9340,9 +9304,6 @@
       <c r="O53" t="n">
         <v>850</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>1.656989878267582</v>
       </c>
@@ -10011,9 +9972,6 @@
       <c r="O57" t="n">
         <v>850</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>1.656989878267582</v>
       </c>
@@ -10682,9 +10640,6 @@
       <c r="O61" t="n">
         <v>928</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>1.809043067096842</v>
       </c>
@@ -11353,9 +11308,6 @@
       <c r="O65" t="n">
         <v>912</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>1.777852669388276</v>
       </c>
@@ -12024,9 +11976,6 @@
       <c r="O69" t="n">
         <v>1141</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>2.22426523659213</v>
       </c>
@@ -12695,9 +12644,6 @@
       <c r="O73" t="n">
         <v>1180</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>2.30029183100676</v>
       </c>
@@ -13366,9 +13312,6 @@
       <c r="O77" t="n">
         <v>971</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>1.892867260938614</v>
       </c>
@@ -14037,9 +13980,6 @@
       <c r="O81" t="n">
         <v>596</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>1.161842314644093</v>
       </c>
@@ -14708,9 +14648,6 @@
       <c r="O85" t="n">
         <v>709</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>1.382124498460842</v>
       </c>
@@ -15379,9 +15316,6 @@
       <c r="O89" t="n">
         <v>966</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>1.883120261654687</v>
       </c>
@@ -16050,9 +15984,6 @@
       <c r="O93" t="n">
         <v>1273</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>2.481586017687802</v>
       </c>
@@ -16721,9 +16652,6 @@
       <c r="O97" t="n">
         <v>1535</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>2.992328780165574</v>
       </c>
@@ -17392,9 +17320,6 @@
       <c r="O101" t="n">
         <v>1318</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>2.559905751961584</v>
       </c>
@@ -18063,9 +17988,6 @@
       <c r="O105" t="n">
         <v>1490</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>2.893975394857936</v>
       </c>
@@ -18734,9 +18656,6 @@
       <c r="O109" t="n">
         <v>1641</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>3.187257465075082</v>
       </c>
@@ -19405,9 +19324,6 @@
       <c r="O113" t="n">
         <v>2956</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>5.741336420939636</v>
       </c>
@@ -20076,9 +19992,6 @@
       <c r="O117" t="n">
         <v>3015</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>5.855930077514548</v>
       </c>
@@ -20747,9 +20660,6 @@
       <c r="O121" t="n">
         <v>2743</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>5.327633898050549</v>
       </c>
@@ -21418,9 +21328,6 @@
       <c r="O125" t="n">
         <v>1627</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>3.160065749955612</v>
       </c>
@@ -22089,9 +21996,6 @@
       <c r="O129" t="n">
         <v>958</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>1.860690220318056</v>
       </c>
@@ -22760,9 +22664,6 @@
       <c r="O133" t="n">
         <v>1431</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>2.779381738283024</v>
       </c>
@@ -23431,9 +23332,6 @@
       <c r="O137" t="n">
         <v>1491</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>2.895917660223613</v>
       </c>
@@ -24102,9 +24000,6 @@
       <c r="O141" t="n">
         <v>1848</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>3.589306395770111</v>
       </c>
@@ -24773,9 +24668,6 @@
       <c r="O145" t="n">
         <v>2320</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>4.506055648369403</v>
       </c>
@@ -25444,9 +25336,6 @@
       <c r="O149" t="n">
         <v>1862</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>3.605669568772377</v>
       </c>
@@ -26115,9 +26004,6 @@
       <c r="O153" t="n">
         <v>1671</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>3.235807652749002</v>
       </c>
@@ -26786,9 +26672,6 @@
       <c r="O157" t="n">
         <v>1754</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>3.39653298798429</v>
       </c>
@@ -27457,9 +27340,6 @@
       <c r="O161" t="n">
         <v>2074</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>4.016196931060101</v>
       </c>
@@ -28128,9 +28008,6 @@
       <c r="O165" t="n">
         <v>1912</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>3.702492059877972</v>
       </c>
@@ -28799,9 +28676,6 @@
       <c r="O169" t="n">
         <v>1479</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>2.864009286903515</v>
       </c>
@@ -29470,9 +29344,6 @@
       <c r="O173" t="n">
         <v>1229</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>2.379896831375537</v>
       </c>
@@ -30141,9 +30012,6 @@
       <c r="O177" t="n">
         <v>666</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>1.289675581526532</v>
       </c>
@@ -30812,9 +30680,6 @@
       <c r="O181" t="n">
         <v>694</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>1.343896176545666</v>
       </c>
@@ -31483,9 +31348,6 @@
       <c r="O185" t="n">
         <v>810</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>1.568524355910647</v>
       </c>
@@ -32154,9 +32016,6 @@
       <c r="O189" t="n">
         <v>842</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>1.630490750218228</v>
       </c>
@@ -32825,9 +32684,6 @@
       <c r="O193" t="n">
         <v>784</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>1.518176660535737</v>
       </c>
@@ -33496,9 +33352,6 @@
       <c r="O197" t="n">
         <v>678</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>1.309693279492448</v>
       </c>
@@ -34167,9 +34020,6 @@
       <c r="O201" t="n">
         <v>629</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>1.215039930384586</v>
       </c>
@@ -34838,9 +34688,6 @@
       <c r="O205" t="n">
         <v>702</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>1.356054103545278</v>
       </c>
@@ -35509,9 +35356,6 @@
       <c r="O209" t="n">
         <v>752</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>1.45263915365534</v>
       </c>
@@ -36180,9 +36024,6 @@
       <c r="O213" t="n">
         <v>788</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>1.522180389734585</v>
       </c>
@@ -36851,9 +36692,6 @@
       <c r="O217" t="n">
         <v>698</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>1.348327299536473</v>
       </c>
@@ -37522,9 +37360,6 @@
       <c r="O221" t="n">
         <v>742</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>1.433322143633328</v>
       </c>
@@ -38193,9 +38028,6 @@
       <c r="O225" t="n">
         <v>464</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.8963092650213802</v>
       </c>
@@ -38864,9 +38696,6 @@
       <c r="O229" t="n">
         <v>498</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0.9619870990962228</v>
       </c>
@@ -39535,9 +39364,6 @@
       <c r="O233" t="n">
         <v>504</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0.9735773051094303</v>
       </c>
@@ -40206,9 +40032,6 @@
       <c r="O237" t="n">
         <v>531</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>1.025733232168864</v>
       </c>
@@ -40876,9 +40699,6 @@
       </c>
       <c r="O241" t="n">
         <v>576</v>
-      </c>
-      <c r="Q241" t="n">
-        <v>0</v>
       </c>
       <c r="R241" t="n">
         <v>1.11265977726792</v>
